--- a/tests/test_data/mock_input_dirty.xlsx
+++ b/tests/test_data/mock_input_dirty.xlsx
@@ -416,13 +416,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="E3:L40"/>
+  <dimension ref="D3:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="3">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Order: 124</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Batch: 10296</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>10296</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Date: 2024-03-21</t>
         </is>
       </c>
     </row>
